--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4270EB4-5178-4089-A53B-D8FE00DBD275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664A83A7-98AE-44E0-B49B-35B5D2C21A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
+    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックステスト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -94,19 +94,6 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>スス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員登録単体テスト</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>タンタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -646,6 +633,59 @@
   </si>
   <si>
     <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事前条件</t>
+    <rPh sb="0" eb="2">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>postgresデータベースに接続できる。</t>
+    <rPh sb="15" eb="17">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リポジトリのホワイトボックステスト  須崎千穂子</t>
+    <rPh sb="19" eb="21">
+      <t>スザキ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>チホコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員登録単体UIテスト 須崎千穂子</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スザキ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>チホコ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -704,7 +744,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -722,6 +762,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1287,16 +1330,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>22225</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>79375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>124160</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1454150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>181310</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1319,7 +1362,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9388475" y="241300"/>
+          <a:off x="79375" y="2813050"/>
           <a:ext cx="6829425" cy="1483060"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1642,45 +1685,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="5"/>
       <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="4" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="4" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -1695,13 +1738,13 @@
       <c r="E4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -1712,76 +1755,76 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
       <c r="G9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <v>7</v>
       </c>
       <c r="B10" t="s">
@@ -1798,43 +1841,43 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="13" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>9</v>
       </c>
       <c r="B13" t="s">
@@ -1849,65 +1892,65 @@
       <c r="E13" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>35</v>
+      <c r="G13" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7"/>
+      <c r="A14" s="8"/>
       <c r="C14" s="1"/>
       <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="G15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="16" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="G16" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1940,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBD947C-1B73-4E6F-A976-09FA645FD6FD}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1950,94 +1993,71 @@
     <col min="5" max="5" width="19.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -2049,61 +2069,137 @@
         <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E12" t="s">
         <v>55</v>
       </c>
-      <c r="E9" t="s">
-        <v>56</v>
+      <c r="F12" s="6">
+        <v>46164</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664A83A7-98AE-44E0-B49B-35B5D2C21A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008CEEE9-8EE0-471D-B80E-228C813E7465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックステスト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="83">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -312,34 +312,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>もう一度社員登録に進み、左記を入力して完了ボタンを押す</t>
-    <rPh sb="2" eb="4">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鈴木五郎</t>
     <rPh sb="0" eb="2">
       <t>スズキ</t>
@@ -354,53 +326,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>手順9のエラーはそのままに、メールアドレスの部分にメールアドレスの形式が不正である旨のポップアップが表示される</t>
-    <rPh sb="0" eb="2">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>フセイ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ムネ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>suzukigorou@csharp.com</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>あいうえおかきくけこさしすせそたちつてとな</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>氏名：20文字以内で入力してください。
-電話番号：電話番号の形式（例: 03-1234-5678）で入力してください。</t>
-    <rPh sb="0" eb="2">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="20" eb="24">
-      <t>デンワバンゴウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -688,12 +618,274 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>カバレッジ計測結果を入れる</t>
+    <rPh sb="5" eb="9">
+      <t>ケイソクケッカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース① 正常系を用いた一通りの流れのチェック</t>
+    <rPh sb="8" eb="11">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒトトオ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース② 入力必須チェック</t>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース④ 名前の文字数チェック（異常系の境界値）</t>
+    <rPh sb="19" eb="21">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース③ 名前の文字数チェック（正常系の境界値：20文字）</t>
+    <rPh sb="8" eb="10">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>キョウカイチ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>を入力して完了ボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あいうえおかきくけこさしすせそたちつてと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>test@csharp.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>090-0000-0010</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑥ 電話番号の形式エラーが正しく出るかチェック</t>
+    <rPh sb="8" eb="10">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑤ メールアドレスの形式エラーが正しく出るかチェック</t>
+    <rPh sb="16" eb="18">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認画面に遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">氏名：20文字以内で入力してください。
+とエラーが出る
+</t>
+    <rPh sb="0" eb="2">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスの部分にメールアドレスの形式が不正である旨のポップアップが表示される</t>
+    <rPh sb="8" eb="10">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>フセイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ムネ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電話番号：電話番号の形式（例: 03-1234-5678）で入力してください。
+とエラー文が出る</t>
+    <rPh sb="44" eb="45">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常系を用いた一通りの流れのチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②入力必須エラーが正しく出るかチェック</t>
+    <rPh sb="9" eb="10">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③名前の文字数チェック（正常系の境界値：20文字）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④名前の文字数チェック（異常系の境界値：21文字）</t>
+    <rPh sb="22" eb="24">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤メールアドレスの形式エラーが正しく出るかチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥電話番号の形式エラーが正しく出るかチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業内容</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手順No.</t>
+    <rPh sb="0" eb="2">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -718,13 +910,43 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -744,7 +966,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -758,9 +980,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -769,7 +988,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -799,14 +1039,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>130</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>539750</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>542926</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -841,60 +1081,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>186117</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>492125</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A2540E-556F-D3D0-763A-B89BB07D420B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15763876" y="2174875"/>
-          <a:ext cx="5520116" cy="1301750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>142062</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1285875</xdr:rowOff>
+      <xdr:colOff>145237</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1282700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -910,7 +1106,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -931,14 +1127,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1233530</xdr:rowOff>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1230355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -954,7 +1150,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -975,14 +1171,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>518282</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1285875</xdr:rowOff>
+      <xdr:colOff>521457</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1282700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -998,7 +1194,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1019,13 +1215,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1544285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1042,7 +1238,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1063,14 +1259,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>406946</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>410121</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1086,7 +1282,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1107,14 +1303,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>301625</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>831246</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>828071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1130,7 +1326,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1151,14 +1347,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>650875</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>643718</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2899</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>640543</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1174,7 +1370,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1194,15 +1390,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>71806</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1444625</xdr:rowOff>
+      <xdr:colOff>103267</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>524164</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1218,15 +1414,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="15970250"/>
-          <a:ext cx="4246931" cy="1444625"/>
+          <a:off x="11603181" y="29452455"/>
+          <a:ext cx="4228170" cy="1444625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1239,58 +1435,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>523328</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1571625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAF1E6E-7829-F2D4-5A53-9650A064E8BD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11588750" y="17700625"/>
-          <a:ext cx="4698453" cy="1571625"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1414974</xdr:rowOff>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1306,7 +1458,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1315,6 +1467,226 @@
         <a:xfrm>
           <a:off x="11588750" y="444500"/>
           <a:ext cx="4683125" cy="1414974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0AEE3F-1073-433F-8964-DBFEBEE77472}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="15401636"/>
+          <a:ext cx="4664364" cy="1414974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB2D75C7-8628-4B3E-942E-EC971EA12D26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="19304000"/>
+          <a:ext cx="4664364" cy="1414974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ABF9636-045A-4457-9330-E96A24995D7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="19523364"/>
+          <a:ext cx="4664364" cy="1414974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85ABE773-31B9-4EF3-ABF4-3858641F9CD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="21913273"/>
+          <a:ext cx="4664364" cy="1414974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1418149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E81B645-FF59-490E-9531-12E0ADE6E68B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="28159364"/>
+          <a:ext cx="4664364" cy="1414974"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1337,7 +1709,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1454150</xdr:colOff>
+      <xdr:colOff>698500</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>181310</xdr:rowOff>
     </xdr:to>
@@ -1362,8 +1734,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="79375" y="2813050"/>
-          <a:ext cx="6829425" cy="1483060"/>
+          <a:off x="79375" y="3041650"/>
+          <a:ext cx="6073775" cy="1483060"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1672,318 +2044,718 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52984F39-C5F9-44A5-B558-1A8AE99FA064}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="54.5" customWidth="1"/>
-    <col min="8" max="8" width="37.25" customWidth="1"/>
+    <col min="7" max="7" width="54.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="37.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" ht="32.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="8">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="8"/>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
+        <v>4</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
+        <v>5</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3">
+        <v>6</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="8">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="8"/>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="5"/>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B23" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="4" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="8">
+    <row r="24" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D24" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="8"/>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G24" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="8"/>
+      <c r="C25" s="7"/>
+      <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3">
+        <v>1</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="8">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="8"/>
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3">
+        <v>1</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="8">
+        <v>2</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="8"/>
+      <c r="B33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3">
+        <v>1</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="8">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="8"/>
+      <c r="B37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3">
+      <c r="G37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3">
+        <v>1</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="8">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="8">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="8"/>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="8"/>
+      <c r="B41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="8">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="8"/>
-      <c r="C14" s="1"/>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>33</v>
+      <c r="G41" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G4:G5"/>
+  <mergeCells count="31">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B31:F31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
-    <hyperlink ref="C16" r:id="rId3" xr:uid="{DBCB28F8-5BCF-4D8B-A883-BBD577ACEFD8}"/>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
+    <hyperlink ref="C20" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
+    <hyperlink ref="C29" r:id="rId3" xr:uid="{D29A384B-38C2-4AD0-BF57-535640A666C4}"/>
+    <hyperlink ref="C33" r:id="rId4" xr:uid="{3521085D-1DF1-4A36-AD28-DFBFAC9A15AC}"/>
+    <hyperlink ref="C41" r:id="rId5" xr:uid="{E445C2AE-7998-4639-8B46-AE1076856BD2}"/>
+    <hyperlink ref="A3" location="ブラックボックステスト!A10" display="①正常系を用いた一通りの流れのチェック" xr:uid="{66CD2A9B-1A7C-410E-B95A-7072E0FFE8D3}"/>
+    <hyperlink ref="A4" location="ブラックボックステスト!A22" display="②入力必須エラーが正しく出るかチェック" xr:uid="{4ECA5742-2FE9-47C3-BA5F-E1F112BBB4B2}"/>
+    <hyperlink ref="A5" location="ブラックボックステスト!A26" display="③名前の文字数チェック（正常系の境界値：20文字）" xr:uid="{032A2E23-2FE2-4B2A-977A-1FBCE98FA354}"/>
+    <hyperlink ref="A6" location="ブラックボックステスト!A30" display="④名前の文字数チェック（異常系の境界値：21文字）" xr:uid="{52F21D79-F2B5-4349-8F1E-554BA27F7329}"/>
+    <hyperlink ref="A7" location="ブラックボックステスト!A34" display="⑤メールアドレスの形式エラーが正しく出るかチェック" xr:uid="{B923A1ED-842F-4F7D-BEE8-808991124684}"/>
+    <hyperlink ref="A8" location="ブラックボックステスト!A38" display="⑥電話番号の形式エラーが正しく出るかチェック" xr:uid="{E8957687-BD25-4FC1-A76F-BD13DED4FAEE}"/>
+    <hyperlink ref="I10" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{D5114FC7-508E-4B07-8734-A9FDF3F0D229}"/>
+    <hyperlink ref="I22" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{534C6B46-2778-4DF1-9222-0775496449A7}"/>
+    <hyperlink ref="I26" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{4D4B8236-F4C8-48D1-9376-80DD9D21E0D7}"/>
+    <hyperlink ref="I30" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{5AAEBD1E-6D3D-4894-B816-7094B8852302}"/>
+    <hyperlink ref="I34" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{49506B4B-EB38-462A-9823-74488B65108D}"/>
+    <hyperlink ref="I38" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{29AC62C4-977F-434C-B418-70D274F23AF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBD947C-1B73-4E6F-A976-09FA645FD6FD}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1995,7 +2767,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2005,194 +2777,199 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+        <v>53</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="6">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="6">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
       <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="6">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="6">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="6">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="6">
+        <v>52</v>
+      </c>
+      <c r="F10" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>46164</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="6">
+        <v>52</v>
+      </c>
+      <c r="F12" s="5">
         <v>46164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008CEEE9-8EE0-471D-B80E-228C813E7465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3984B783-2F51-4C0B-B8C2-2C5F461A3F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -256,31 +256,6 @@
   </si>
   <si>
     <t>テスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>を入力して完了を押し、確認画面で登録を押す</t>
-    <rPh sb="1" eb="3">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>オ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -877,6 +852,41 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経理部</t>
+    <rPh sb="0" eb="3">
+      <t>ケイリブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>を入力または選択して完了を押し、確認画面で登録を押す</t>
+    <rPh sb="1" eb="3">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -994,23 +1004,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1043,17 +1053,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>130</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1916546</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>542926</xdr:rowOff>
+      <xdr:rowOff>544675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C31824-C35D-38DA-3A78-F36F2713ACFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{571514F8-07FF-A7C6-7966-BAF0DC2ED72A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1069,8 +1079,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="2174875"/>
-          <a:ext cx="4175255" cy="1349375"/>
+          <a:off x="11568545" y="4814455"/>
+          <a:ext cx="1916546" cy="1352856"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1081,23 +1091,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>145237</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1282700</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>44949</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>588819</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="16" name="図 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2FA8940-33B6-1B0A-4BC7-0200854DAB35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8724A15-B2A4-5755-2099-F979788260CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1113,8 +1123,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588751" y="3794126"/>
-          <a:ext cx="4317186" cy="1285874"/>
+          <a:off x="14408727" y="4814455"/>
+          <a:ext cx="2677313" cy="1397000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1127,21 +1137,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1230355</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2147455</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1403497</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="20" name="図 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93529FC-3D3B-9346-68A9-42FEA1FCAE04}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F69E4B8-7A81-E39D-4BB0-3BF83C6B3519}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1157,8 +1167,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="5524500"/>
-          <a:ext cx="5476875" cy="1233530"/>
+          <a:off x="11568545" y="6430819"/>
+          <a:ext cx="2147455" cy="1403496"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1171,21 +1181,65 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2677313</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1397000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{900216D5-F570-407E-90E4-6F3CA4580017}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="8162636"/>
+          <a:ext cx="2677313" cy="1397000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>521457</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2817091</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1282700</xdr:rowOff>
+      <xdr:rowOff>1504929</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94B92347-77EF-09E5-DC97-1AE36100DB8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADB5171C-1EAB-A559-F4C6-054187D8DB8F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1201,8 +1255,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="7254875"/>
-          <a:ext cx="5360157" cy="1285875"/>
+          <a:off x="11568545" y="9894455"/>
+          <a:ext cx="2817091" cy="1504929"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1214,22 +1268,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2389910</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1544285</xdr:rowOff>
+      <xdr:rowOff>1570597</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{430850A8-A8C7-CA2B-7332-5948C9ABCB16}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56FC2CC1-867E-3C8A-8799-E18D128E21A7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1245,8 +1299,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588751" y="8985250"/>
-          <a:ext cx="5095874" cy="1544285"/>
+          <a:off x="11568545" y="11626273"/>
+          <a:ext cx="2389910" cy="1570597"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1257,23 +1311,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323273</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>410121</xdr:rowOff>
+      <xdr:rowOff>639403</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78BCC29A-F802-F332-4DCB-894A7DD7CEE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83AD618B-B489-DEEF-6151-A911116A6971}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1289,8 +1343,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="10715625"/>
-          <a:ext cx="5413375" cy="1375321"/>
+          <a:off x="14408727" y="13358092"/>
+          <a:ext cx="2955637" cy="1609220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1303,21 +1357,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>301625</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>828071</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2370891</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>635001</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="25" name="図 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A870AC8B-4986-D70C-2ADC-5BE5B42FF3DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74097708-808D-9BC5-8EAE-151F5FF4C174}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1333,8 +1387,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="12652375"/>
-          <a:ext cx="5143500" cy="831246"/>
+          <a:off x="11568545" y="13358092"/>
+          <a:ext cx="2370891" cy="1604818"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1347,21 +1401,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>2899</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>640543</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2631304</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1443181</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="26" name="図 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45CE4387-BA8F-0DB0-B6CD-CFA263D80DC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82AEB82-86DB-DA09-90A7-F70BE4772CF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1377,8 +1431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="14382750"/>
-          <a:ext cx="4159250" cy="1437468"/>
+          <a:off x="11568545" y="15297727"/>
+          <a:ext cx="2631304" cy="1443181"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1390,22 +1444,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>103267</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>524164</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2262911</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="27" name="図 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B8B24EE-B495-094B-4174-1F200F9139D5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CA6C0A7-309C-1777-4AB9-DAAFAFACCDE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1421,8 +1475,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11603181" y="29452455"/>
-          <a:ext cx="4228170" cy="1444625"/>
+          <a:off x="11568546" y="17606818"/>
+          <a:ext cx="2262910" cy="1606034"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1434,22 +1488,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1951183</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>441</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="28" name="図 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D511AF70-9392-23DD-30E5-EF8236DE4548}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46120387-4A9A-D8C6-06AD-3EDE0796D509}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1465,8 +1519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11588750" y="444500"/>
-          <a:ext cx="4683125" cy="1414974"/>
+          <a:off x="11568546" y="19338636"/>
+          <a:ext cx="1951182" cy="1593714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1479,21 +1533,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2516910</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>656389</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
+        <xdr:cNvPr id="29" name="図 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0AEE3F-1073-433F-8964-DBFEBEE77472}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C555AA-2EBC-83BB-2D86-6CE416B69EA9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1502,15 +1556,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="15401636"/>
-          <a:ext cx="4664364" cy="1414974"/>
+          <a:off x="11568545" y="23448818"/>
+          <a:ext cx="2516910" cy="1626207"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1523,21 +1577,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2124364</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>791166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
+        <xdr:cNvPr id="30" name="図 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB2D75C7-8628-4B3E-942E-EC971EA12D26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8B52814-CA13-AAEE-2F6E-774EFF741C0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1546,15 +1600,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="19304000"/>
-          <a:ext cx="4664364" cy="1414974"/>
+          <a:off x="11568545" y="27732182"/>
+          <a:ext cx="2124364" cy="1622439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1571,17 +1625,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2262910</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
+        <xdr:cNvPr id="31" name="図 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ABF9636-045A-4457-9330-E96A24995D7C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1E654DB-4B4B-4A32-BB70-FFBECEE6FC91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1590,15 +1644,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="19523364"/>
-          <a:ext cx="4664364" cy="1414974"/>
+          <a:off x="11568545" y="21728545"/>
+          <a:ext cx="2262910" cy="1606034"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1615,17 +1669,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2262910</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
+        <xdr:cNvPr id="32" name="図 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85ABE773-31B9-4EF3-ABF4-3858641F9CD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{954211D0-0025-42EE-988E-631CBC32838B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1634,15 +1688,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="21913273"/>
-          <a:ext cx="4664364" cy="1414974"/>
+          <a:off x="11568545" y="26011909"/>
+          <a:ext cx="2262910" cy="1606034"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1655,21 +1709,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>1418149</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2563091</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>832854</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
+        <xdr:cNvPr id="33" name="図 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E81B645-FF59-490E-9531-12E0ADE6E68B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{187F551D-EA74-887B-ED7B-E1FA28EC1B45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1678,15 +1732,147 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="28159364"/>
-          <a:ext cx="4664364" cy="1414974"/>
+          <a:off x="11568545" y="31588364"/>
+          <a:ext cx="2563091" cy="1825763"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2262910</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1606034</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC7D840C-77C9-457B-AB4A-7F41A962B73C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="29972000"/>
+          <a:ext cx="2262910" cy="1606034"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2262910</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1606034</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="図 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872C51D0-BBAC-4527-BA8D-6CE0346FA74E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="34313091"/>
+          <a:ext cx="2262910" cy="1606034"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1893455</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>676825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="図 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A83F2197-0C51-A9DA-E49D-83DBFA87A4B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="36044909"/>
+          <a:ext cx="1893455" cy="1473461"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2057,19 +2243,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2080,7 +2266,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2091,7 +2277,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2102,7 +2288,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2113,7 +2299,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2124,7 +2310,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2135,7 +2321,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2152,32 +2338,32 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="32.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+    <row r="10" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
       <c r="I10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="B11" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="4" t="s">
         <v>8</v>
       </c>
@@ -2189,13 +2375,13 @@
       <c r="A12" s="3">
         <v>1</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="6" t="s">
         <v>10</v>
       </c>
@@ -2216,10 +2402,10 @@
       <c r="E13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8"/>
@@ -2236,22 +2422,22 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2260,13 +2446,13 @@
       <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2275,13 +2461,13 @@
       <c r="A17" s="3">
         <v>5</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="2" t="s">
         <v>19</v>
       </c>
@@ -2290,13 +2476,13 @@
       <c r="A18" s="3">
         <v>6</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
       <c r="G18" s="6" t="s">
         <v>10</v>
       </c>
@@ -2321,19 +2507,19 @@
     <row r="20" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2343,43 +2529,43 @@
       <c r="A21" s="3">
         <v>8</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="B21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="A22" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
         <v>1</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
       <c r="G23" s="6" t="s">
         <v>10</v>
       </c>
@@ -2400,8 +2586,8 @@
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>31</v>
+      <c r="G24" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2411,36 +2597,36 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="A26" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
       <c r="I26" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
         <v>1</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
       <c r="G27" s="6" t="s">
         <v>10</v>
       </c>
@@ -2462,55 +2648,55 @@
         <v>3</v>
       </c>
       <c r="F28" s="6"/>
-      <c r="G28" s="10" t="s">
-        <v>69</v>
+      <c r="G28" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8"/>
       <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29" s="10"/>
+        <v>62</v>
+      </c>
+      <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
+      <c r="A30" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
       <c r="I30" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
         <v>1</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
       <c r="G31" s="6" t="s">
         <v>10</v>
       </c>
@@ -2532,55 +2718,55 @@
         <v>3</v>
       </c>
       <c r="F32" s="6"/>
-      <c r="G32" s="10" t="s">
-        <v>70</v>
+      <c r="G32" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8"/>
       <c r="B33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33" s="10"/>
+        <v>62</v>
+      </c>
+      <c r="G33" s="12"/>
     </row>
     <row r="34" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
+      <c r="A34" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
         <v>1</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
       <c r="G35" s="6" t="s">
         <v>10</v>
       </c>
@@ -2607,13 +2793,13 @@
     <row r="37" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8"/>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
@@ -2622,35 +2808,35 @@
         <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+      <c r="A38" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
       <c r="I38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
         <v>1</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
       <c r="G39" s="6" t="s">
         <v>10</v>
       </c>
@@ -2676,10 +2862,10 @@
     <row r="41" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="8"/>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>21</v>
@@ -2691,26 +2877,11 @@
         <v>12</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B11:F11"/>
@@ -2727,6 +2898,21 @@
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -2767,7 +2953,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2777,10 +2963,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -2789,39 +2975,39 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="5">
         <v>46164</v>
@@ -2829,19 +3015,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5">
         <v>46164</v>
@@ -2849,19 +3035,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="5">
         <v>46164</v>
@@ -2869,19 +3055,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5">
         <v>46164</v>
@@ -2889,19 +3075,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5">
         <v>46164</v>
@@ -2909,19 +3095,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="5">
         <v>46164</v>
@@ -2929,19 +3115,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="5">
         <v>46164</v>
@@ -2949,19 +3135,19 @@
     </row>
     <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" t="s">
         <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
       </c>
       <c r="F12" s="5">
         <v>46164</v>
@@ -2969,7 +3155,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="E13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3984B783-2F51-4C0B-B8C2-2C5F461A3F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CC2ACD-E974-46C9-ACBF-F521C5CA738E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
+    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックステスト" sheetId="1" r:id="rId1"/>
-    <sheet name="ホワイトボックステスト（インフラのリポジトリのみ）" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="71">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -337,244 +336,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>対象リポジトリ</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対象メソッド</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>条件</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テスト判定</t>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Department</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Employee</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FindAll</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FindById</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Create</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に何も入っていないとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力したidに合致する部署が存在するとき</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガッチ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力したidに合致する部署が存在しないとき</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガッチ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に部署が入っているとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象と同じ部署を取得する</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>InternalExceptionを返す</t>
-    <rPh sb="18" eb="19">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>該当部署を取得する</t>
-    <rPh sb="0" eb="4">
-      <t>ガイトウブショ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>すでに存在している社員をAddしたとき</t>
-    <rPh sb="3" eb="5">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に社員が入っているとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>未登録の社員をAddしたとき</t>
-    <rPh sb="0" eb="3">
-      <t>ミトウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社員が追加され追加社員も含めて社員情報が合致する</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガッチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>○</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>事前条件</t>
-    <rPh sb="0" eb="2">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日付</t>
-    <rPh sb="0" eb="2">
-      <t>ヒヅケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>postgresデータベースに接続できる。</t>
-    <rPh sb="15" eb="17">
-      <t>セツゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リポジトリのホワイトボックステスト  須崎千穂子</t>
-    <rPh sb="19" eb="21">
-      <t>スザキ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>チホコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>従業員登録単体UIテスト 須崎千穂子</t>
     <rPh sb="0" eb="3">
       <t>ジュウギョウイン</t>
@@ -590,16 +351,6 @@
     </rPh>
     <rPh sb="15" eb="18">
       <t>チホコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カバレッジ計測結果を入れる</t>
-    <rPh sb="5" eb="9">
-      <t>ケイソクケッカ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>イ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -887,6 +638,156 @@
     </rPh>
     <rPh sb="24" eb="25">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>田中太郎</t>
+  </si>
+  <si>
+    <t>tanakatarou@csharp.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>090-0000-0003</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部に「同じメールアドレスがすでに登録されています。」とエラーが出る</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tanaka@csharp.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>090-0000-0001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部に「同じ電話番号がすでに登録されています。」とエラーが出る</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑦ 同じメールアドレスが登録されていた場合</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑧ 同じ電話番号が登録されていた場合</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑨ 同じメールアドレスが登録されていた場合</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑦同じメールアドレスが登録されていた場合のエラーチェック</t>
+    <rPh sb="1" eb="2">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑧同じ電話番号が登録されていた場合のエラーチェック</t>
+    <rPh sb="1" eb="2">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑨同じメールアドレスかつ同じ電話番号が登録されていた場合のエラーチェック</t>
+    <rPh sb="1" eb="2">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -976,7 +877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -991,9 +892,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1022,9 +920,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1049,14 +944,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1916546</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>544675</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>544676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1093,14 +988,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>44949</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>588819</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>588820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1137,13 +1032,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2147455</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1403497</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1181,13 +1076,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2677313</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1397000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1225,13 +1120,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2817091</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1504929</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1269,13 +1164,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2389910</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1570597</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1313,13 +1208,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>323273</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>639403</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1357,13 +1252,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2370891</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>635001</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1401,13 +1296,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2631304</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>1443181</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1445,13 +1340,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2262911</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1489,13 +1384,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1951183</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>441</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1533,14 +1428,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2516910</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>656389</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>656390</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1577,13 +1472,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2124364</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>791166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1621,13 +1516,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1665,13 +1560,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1709,13 +1604,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2563091</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>832854</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1753,13 +1648,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1797,13 +1692,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>1606034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1841,14 +1736,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1893455</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>676825</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>676826</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1873,55 +1768,6 @@
         <a:xfrm>
           <a:off x="11568545" y="36044909"/>
           <a:ext cx="1893455" cy="1473461"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>79375</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>698500</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>181310</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B87D4EBE-0363-33C7-F15F-E105D2A184E1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="79375" y="3041650"/>
-          <a:ext cx="6073775" cy="1483060"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2230,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52984F39-C5F9-44A5-B558-1A8AE99FA064}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.83203125" style="2" customWidth="1"/>
@@ -2243,19 +2089,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2266,7 +2112,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2277,7 +2123,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2288,7 +2134,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2299,7 +2145,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2310,7 +2156,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2321,7 +2167,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2331,6 +2177,9 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2338,833 +2187,858 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="1" t="s">
-        <v>78</v>
-      </c>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="4" t="s">
+      <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3">
-        <v>1</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="8">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="8"/>
-      <c r="B14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3">
+      <c r="G16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3">
+      <c r="C17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
-        <v>6</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="8">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="8"/>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>83</v>
-      </c>
+    </row>
+    <row r="20" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
+        <v>6</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3">
         <v>8</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="2" t="s">
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="13" t="s">
+    <row r="25" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3">
+        <v>1</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="C28" s="6"/>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3">
+        <v>1</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3">
+        <v>1</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7">
+        <v>2</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3">
+        <v>1</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3">
+        <v>1</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7">
+        <v>2</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3">
+        <v>1</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7">
+        <v>2</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3">
+      <c r="D48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="38.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3">
         <v>1</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6" t="s">
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="8">
+    <row r="51" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="7">
         <v>2</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="E25" s="2" t="s">
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7"/>
+      <c r="B52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="13" t="s">
+      <c r="F52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3">
+    </row>
+    <row r="53" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3">
         <v>1</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B54" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6" t="s">
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="8">
+    <row r="55" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="7">
         <v>2</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="8"/>
-      <c r="B29" s="2" t="s">
+      <c r="F55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="7"/>
+      <c r="B56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="3">
-        <v>1</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="8">
-        <v>2</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="8"/>
-      <c r="B33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3">
-        <v>1</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="8">
-        <v>2</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="8"/>
-      <c r="B37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3">
-        <v>1</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="8">
-        <v>2</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="8"/>
-      <c r="B41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>71</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A40:A41"/>
+  <mergeCells count="40">
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
-    <hyperlink ref="C20" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
-    <hyperlink ref="C29" r:id="rId3" xr:uid="{D29A384B-38C2-4AD0-BF57-535640A666C4}"/>
-    <hyperlink ref="C33" r:id="rId4" xr:uid="{3521085D-1DF1-4A36-AD28-DFBFAC9A15AC}"/>
-    <hyperlink ref="C41" r:id="rId5" xr:uid="{E445C2AE-7998-4639-8B46-AE1076856BD2}"/>
+    <hyperlink ref="C17" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
+    <hyperlink ref="C23" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
+    <hyperlink ref="C32" r:id="rId3" xr:uid="{D29A384B-38C2-4AD0-BF57-535640A666C4}"/>
+    <hyperlink ref="C36" r:id="rId4" xr:uid="{3521085D-1DF1-4A36-AD28-DFBFAC9A15AC}"/>
+    <hyperlink ref="C44" r:id="rId5" xr:uid="{E445C2AE-7998-4639-8B46-AE1076856BD2}"/>
     <hyperlink ref="A3" location="ブラックボックステスト!A10" display="①正常系を用いた一通りの流れのチェック" xr:uid="{66CD2A9B-1A7C-410E-B95A-7072E0FFE8D3}"/>
     <hyperlink ref="A4" location="ブラックボックステスト!A22" display="②入力必須エラーが正しく出るかチェック" xr:uid="{4ECA5742-2FE9-47C3-BA5F-E1F112BBB4B2}"/>
     <hyperlink ref="A5" location="ブラックボックステスト!A26" display="③名前の文字数チェック（正常系の境界値：20文字）" xr:uid="{032A2E23-2FE2-4B2A-977A-1FBCE98FA354}"/>
     <hyperlink ref="A6" location="ブラックボックステスト!A30" display="④名前の文字数チェック（異常系の境界値：21文字）" xr:uid="{52F21D79-F2B5-4349-8F1E-554BA27F7329}"/>
     <hyperlink ref="A7" location="ブラックボックステスト!A34" display="⑤メールアドレスの形式エラーが正しく出るかチェック" xr:uid="{B923A1ED-842F-4F7D-BEE8-808991124684}"/>
     <hyperlink ref="A8" location="ブラックボックステスト!A38" display="⑥電話番号の形式エラーが正しく出るかチェック" xr:uid="{E8957687-BD25-4FC1-A76F-BD13DED4FAEE}"/>
-    <hyperlink ref="I10" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{D5114FC7-508E-4B07-8734-A9FDF3F0D229}"/>
-    <hyperlink ref="I22" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{534C6B46-2778-4DF1-9222-0775496449A7}"/>
-    <hyperlink ref="I26" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{4D4B8236-F4C8-48D1-9376-80DD9D21E0D7}"/>
-    <hyperlink ref="I30" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{5AAEBD1E-6D3D-4894-B816-7094B8852302}"/>
-    <hyperlink ref="I34" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{49506B4B-EB38-462A-9823-74488B65108D}"/>
-    <hyperlink ref="I38" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{29AC62C4-977F-434C-B418-70D274F23AF7}"/>
+    <hyperlink ref="I13" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{D5114FC7-508E-4B07-8734-A9FDF3F0D229}"/>
+    <hyperlink ref="I25" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{534C6B46-2778-4DF1-9222-0775496449A7}"/>
+    <hyperlink ref="I29" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{4D4B8236-F4C8-48D1-9376-80DD9D21E0D7}"/>
+    <hyperlink ref="I33" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{5AAEBD1E-6D3D-4894-B816-7094B8852302}"/>
+    <hyperlink ref="I37" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{49506B4B-EB38-462A-9823-74488B65108D}"/>
+    <hyperlink ref="I41" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{29AC62C4-977F-434C-B418-70D274F23AF7}"/>
+    <hyperlink ref="C48" r:id="rId6" xr:uid="{6798A490-9A31-48A6-BCA0-BA97DDE1492B}"/>
+    <hyperlink ref="C52" r:id="rId7" xr:uid="{CD8DEF8E-ACB6-4A14-B9B8-F6E647E4F9B1}"/>
+    <hyperlink ref="C56" r:id="rId8" xr:uid="{4B17CFFE-5E79-43D3-96DD-F4D2C3AA02D6}"/>
+    <hyperlink ref="A9" location="ブラックボックステスト!A45" display="⑦同じメールアドレスが登録されていた場合のエラーチェック" xr:uid="{0F02ECD7-A6BA-44BF-A55F-DCC56CECE266}"/>
+    <hyperlink ref="A10" location="ブラックボックステスト!A49" display="⑧同じ電話番号が登録されていた場合のエラーチェック" xr:uid="{298276B0-CE79-4A4C-9132-EFB29453C126}"/>
+    <hyperlink ref="A11" location="ブラックボックステスト!A53" display="⑨同じメールアドレスかつ同じ電話番号が登録されていた場合のエラーチェック" xr:uid="{7C40F3E6-DC6A-4C80-AD6D-FEA1A2DEB489}"/>
+    <hyperlink ref="I45" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{58481281-7845-4E0B-B26B-4C4A31D3B3D1}"/>
+    <hyperlink ref="I49" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{A6993151-D69B-4DC2-A480-1C1411EAF989}"/>
+    <hyperlink ref="I53" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{85C4F0E6-D6A6-4489-8DD4-16965B4292FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId6"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBD947C-1B73-4E6F-A976-09FA645FD6FD}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="16.9140625" customWidth="1"/>
-    <col min="3" max="3" width="39.4140625" customWidth="1"/>
-    <col min="4" max="4" width="31.9140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.4140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CC2ACD-E974-46C9-ACBF-F521C5CA738E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FED9D80-042C-4F53-A6EC-D53F4F9EBE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックステスト" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -66,20 +66,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鈴木三郎</t>
-    <rPh sb="0" eb="2">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>サブロウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>suzukisaburou@csharp.com</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>090-0000-0012</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -107,25 +93,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の「社員登録」ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>従業員登録(入力)画面に遷移する</t>
     <rPh sb="9" eb="11">
       <t>ガメン</t>
@@ -247,13 +214,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ホームボタンに戻る</t>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テスト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -273,16 +233,6 @@
   </si>
   <si>
     <t>090-0000-0013</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メニューに戻るボタンを押す</t>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -731,19 +681,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テストケース⑨ 同じメールアドレスが登録されていた場合</t>
-    <rPh sb="8" eb="9">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>⑦同じメールアドレスが登録されていた場合のエラーチェック</t>
     <rPh sb="1" eb="2">
       <t>オナ</t>
@@ -788,6 +725,171 @@
     </rPh>
     <rPh sb="26" eb="28">
       <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑩ホーム画面の「従業員一覧」から登録画面への遷移チェック</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面の従業員管理ボタンを押す</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員一覧に遷移する</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規従業員の登録ボタンを押す</t>
+    <rPh sb="0" eb="5">
+      <t>シンキジュウギョウイン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録画面に遷移する</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の「従業員登録」ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高橋太郎</t>
+    <rPh sb="0" eb="2">
+      <t>タカハシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>takahashi@csharp.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員一覧を確認するボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員一覧に遷移する</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース⑨ 同じメールアドレス&amp;電話番号が登録されていた場合</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じメールアドレスのエラーと同じ電話番号のエラーが両方出る</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>デ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -877,7 +979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -888,9 +990,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -899,11 +998,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -912,13 +1017,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -949,16 +1054,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1916546</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>544676</xdr:rowOff>
+      <xdr:colOff>2609273</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1576731</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{571514F8-07FF-A7C6-7966-BAF0DC2ED72A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E0B3FC4-B033-C6EA-B13A-5BB510C64F65}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,8 +1079,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="4814455"/>
-          <a:ext cx="1916546" cy="1352856"/>
+          <a:off x="11568545" y="4006273"/>
+          <a:ext cx="2609273" cy="1576731"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -986,23 +1091,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>44949</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>588820</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2817091</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>470085</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8724A15-B2A4-5755-2099-F979788260CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92E89483-DD7A-DD2E-41A0-53DEF3D00764}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1018,8 +1123,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14408727" y="4814455"/>
-          <a:ext cx="2677313" cy="1397000"/>
+          <a:off x="11568545" y="5738092"/>
+          <a:ext cx="2817091" cy="1278266"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1032,21 +1137,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2147455</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1403497</xdr:rowOff>
+      <xdr:colOff>2574839</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1581727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F69E4B8-7A81-E39D-4BB0-3BF83C6B3519}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01694564-A783-875C-02C7-8750AC97DA15}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1062,8 +1167,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="6430819"/>
-          <a:ext cx="2147455" cy="1403496"/>
+          <a:off x="11568545" y="7354455"/>
+          <a:ext cx="2574839" cy="1581727"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1076,21 +1181,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2677313</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1397000</xdr:rowOff>
+      <xdr:colOff>2817091</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1278266</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{900216D5-F570-407E-90E4-6F3CA4580017}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F103663-B27B-4AB5-AC21-F7DE3DD3FCA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1106,8 +1211,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="8162636"/>
-          <a:ext cx="2677313" cy="1397000"/>
+          <a:off x="11568545" y="9086273"/>
+          <a:ext cx="2817091" cy="1278266"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1120,21 +1225,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2817091</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1504929</xdr:rowOff>
+      <xdr:colOff>2792145</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1339273</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADB5171C-1EAB-A559-F4C6-054187D8DB8F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95BC963-C140-DFD5-0F0C-EA08271EBD67}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1150,8 +1255,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="9894455"/>
-          <a:ext cx="2817091" cy="1504929"/>
+          <a:off x="11568545" y="10818091"/>
+          <a:ext cx="2792145" cy="1339273"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1164,21 +1269,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2389910</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1570597</xdr:rowOff>
+      <xdr:colOff>2620819</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1612813</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56FC2CC1-867E-3C8A-8799-E18D128E21A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{180C5E17-5905-0478-A8AF-8435DBFD309F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1194,8 +1299,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="11626273"/>
-          <a:ext cx="2389910" cy="1570597"/>
+          <a:off x="11568545" y="12549910"/>
+          <a:ext cx="2620819" cy="1612812"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1206,23 +1311,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>323273</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>639403</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2690091</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>459025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83AD618B-B489-DEEF-6151-A911116A6971}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED64F671-2A0F-22E0-FB1D-4A686371F009}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1238,8 +1343,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14408727" y="13358092"/>
-          <a:ext cx="2955637" cy="1609220"/>
+          <a:off x="11568545" y="14281727"/>
+          <a:ext cx="2690091" cy="1301843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1252,21 +1357,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2370891</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>635001</xdr:rowOff>
+      <xdr:colOff>2528455</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1604320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
+        <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74097708-808D-9BC5-8EAE-151F5FF4C174}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98CD5786-8E25-F8E3-D203-7233D78E5BFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1282,8 +1387,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="13358092"/>
-          <a:ext cx="2370891" cy="1604818"/>
+          <a:off x="11568545" y="15967364"/>
+          <a:ext cx="2528455" cy="1604320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1296,21 +1401,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2631304</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1443181</xdr:rowOff>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82AEB82-86DB-DA09-90A7-F70BE4772CF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D8AA52-0923-B109-3FDC-EA3B1BF0C045}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1326,8 +1431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="15297727"/>
-          <a:ext cx="2631304" cy="1443181"/>
+          <a:off x="11568545" y="18276455"/>
+          <a:ext cx="2574637" cy="1618019"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1339,22 +1444,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2262911</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1606034</xdr:rowOff>
+      <xdr:colOff>2736273</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>891093</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
+        <xdr:cNvPr id="14" name="図 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CA6C0A7-309C-1777-4AB9-DAAFAFACCDE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A27E57CA-D631-E237-3EC7-DE2366321078}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1370,8 +1475,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568546" y="17606818"/>
-          <a:ext cx="2262910" cy="1606034"/>
+          <a:off x="11568545" y="20008273"/>
+          <a:ext cx="2736273" cy="1918638"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1383,22 +1488,330 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1951183</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>441</xdr:rowOff>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
+        <xdr:cNvPr id="15" name="図 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46120387-4A9A-D8C6-06AD-3EDE0796D509}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11BCF753-276F-4BF4-AE46-37DB7684307B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="22860000"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43DFC006-61B6-4E6D-89B2-D222E5CF4091}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="27143364"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1656</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69D19386-E921-4EAB-8281-A10D0C154766}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="31103455"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E35BA470-B1ED-4229-B3D2-CAF38CD33B31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="35444545"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="図 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52836F56-21F4-4431-9354-719A5D685058}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="39219909"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="図 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F217B490-4674-49FF-BAF4-45F03A62543A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="42487273"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2574637</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1618019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="図 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBFFD681-EAB9-4A4B-9D24-3679CE890775}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568545" y="46666727"/>
+          <a:ext cx="2574637" cy="1618019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2805547</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>475371</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="図 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7779188B-268D-FBAD-419A-F7C38A52062C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1414,8 +1827,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568546" y="19338636"/>
-          <a:ext cx="1951182" cy="1593714"/>
+          <a:off x="11568546" y="24580273"/>
+          <a:ext cx="2805546" cy="1445189"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1428,21 +1841,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2516910</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>656390</xdr:rowOff>
+      <xdr:colOff>2043546</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>765582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
+        <xdr:cNvPr id="42" name="図 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C555AA-2EBC-83BB-2D86-6CE416B69EA9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951DCF5A-1E6B-98E0-F7FC-525AF5065C75}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1458,8 +1871,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="23448818"/>
-          <a:ext cx="2516910" cy="1626207"/>
+          <a:off x="11568545" y="28863636"/>
+          <a:ext cx="2043546" cy="1596855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1472,21 +1885,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2124364</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>791166</xdr:rowOff>
+      <xdr:colOff>2765066</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>577274</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
+        <xdr:cNvPr id="43" name="図 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8B52814-CA13-AAEE-2F6E-774EFF741C0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE66843-53BF-9D32-9322-A42BDE4552E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1502,8 +1915,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="27732182"/>
-          <a:ext cx="2124364" cy="1622439"/>
+          <a:off x="11568545" y="32719819"/>
+          <a:ext cx="2765066" cy="1570182"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1516,109 +1929,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1606034</xdr:rowOff>
+      <xdr:colOff>2378364</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>706761</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
+        <xdr:cNvPr id="44" name="図 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1E654DB-4B4B-4A32-BB70-FFBECEE6FC91}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="21728545"/>
-          <a:ext cx="2262910" cy="1606034"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1606034</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="図 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{954211D0-0025-42EE-988E-631CBC32838B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="26011909"/>
-          <a:ext cx="2262910" cy="1606034"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2563091</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>832854</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="図 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{187F551D-EA74-887B-ED7B-E1FA28EC1B45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D2D219-EAD6-75B6-378C-8EA64635821E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1634,8 +1959,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="31588364"/>
-          <a:ext cx="2563091" cy="1825763"/>
+          <a:off x="11568545" y="37176364"/>
+          <a:ext cx="2378364" cy="1503397"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1648,109 +1973,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>1606034</xdr:rowOff>
+      <xdr:colOff>1951182</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>600900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
+        <xdr:cNvPr id="45" name="図 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC7D840C-77C9-457B-AB4A-7F41A962B73C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="29972000"/>
-          <a:ext cx="2262910" cy="1606034"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2262910</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>1606034</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="図 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872C51D0-BBAC-4527-BA8D-6CE0346FA74E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="34313091"/>
-          <a:ext cx="2262910" cy="1606034"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1893455</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>676826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A83F2197-0C51-A9DA-E49D-83DBFA87A4B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E84E97F5-62E9-78FD-BD9E-1B2D265B337F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1766,8 +2003,184 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="36044909"/>
-          <a:ext cx="1893455" cy="1473461"/>
+          <a:off x="11568545" y="40974818"/>
+          <a:ext cx="1951182" cy="1270537"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57728</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2670993</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>796636</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="図 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE49798D-A44C-9251-C926-62AE11A119FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11626273" y="44704000"/>
+          <a:ext cx="2613265" cy="1685636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2343729</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>835998</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4363D7AA-8D68-297B-1945-D3BE4EF0A64F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568546" y="48918091"/>
+          <a:ext cx="2343728" cy="1701907"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2678547</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1281856</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="図 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57D82C9A-E1CE-0C6B-5930-6B886CAAF569}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568546" y="51030909"/>
+          <a:ext cx="2678546" cy="1281856"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2793057</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>11546</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="図 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BB69F41-9CEA-E2AF-BA36-1129497FD459}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11568546" y="52716545"/>
+          <a:ext cx="2793056" cy="1604819"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2076,9 +2489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52984F39-C5F9-44A5-B558-1A8AE99FA064}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
+    <col min="1" max="1" width="8.6640625" style="12"/>
     <col min="2" max="2" width="14.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
@@ -2089,954 +2503,1015 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="A9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="A10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="A11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="A12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="12">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="14">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="14"/>
+      <c r="B18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="F18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="12">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="12">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="12">
+        <v>5</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="12">
+        <v>6</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="66.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="14">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="D23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="66.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="14"/>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="12">
+        <v>8</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="12">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="80.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="14">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="80.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="14"/>
+      <c r="C29" s="5"/>
+      <c r="E29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="12">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="14">
+        <v>2</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="14"/>
+      <c r="B33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="12">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="14">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="14"/>
+      <c r="B37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="12">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="14">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="14"/>
+      <c r="B41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7">
+      <c r="G41" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="12">
+        <v>1</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="14">
         <v>2</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="14"/>
+      <c r="B45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="12">
+        <v>1</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7"/>
-      <c r="B17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2" t="s">
+    </row>
+    <row r="48" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="14">
+        <v>2</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="14"/>
+      <c r="B49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="38.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="150" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="12">
+        <v>1</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="14">
+        <v>2</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="14"/>
+      <c r="B53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3">
+      <c r="D53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="148" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="12">
+        <v>1</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="68.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="14">
+        <v>2</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3">
-        <v>4</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3">
-        <v>5</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3">
-        <v>6</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="7">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" ht="68.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="14"/>
+      <c r="B57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="133" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="12">
         <v>1</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="B59" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="125" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="12">
         <v>2</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7"/>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3">
-        <v>8</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3">
-        <v>1</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="7">
-        <v>2</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="7"/>
-      <c r="C28" s="6"/>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="3">
-        <v>1</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="7">
-        <v>2</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="7"/>
-      <c r="B32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3">
-        <v>1</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="7">
-        <v>2</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="7"/>
-      <c r="B36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" s="11"/>
-    </row>
-    <row r="37" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3">
-        <v>1</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="7">
-        <v>2</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7"/>
-      <c r="B40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3">
-        <v>1</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="7">
-        <v>2</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="7"/>
-      <c r="B44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3">
-        <v>1</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="7">
-        <v>2</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="7"/>
-      <c r="B48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="38.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="3">
-        <v>1</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="7">
-        <v>2</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F51" s="5"/>
-    </row>
-    <row r="52" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="7"/>
-      <c r="B52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="3">
-        <v>1</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="7">
-        <v>2</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F55" s="5"/>
-    </row>
-    <row r="56" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="7"/>
-      <c r="B56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>64</v>
+      <c r="B60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B18:F18"/>
+  <mergeCells count="43">
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="B51:F51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C17" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
-    <hyperlink ref="C23" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
-    <hyperlink ref="C32" r:id="rId3" xr:uid="{D29A384B-38C2-4AD0-BF57-535640A666C4}"/>
-    <hyperlink ref="C36" r:id="rId4" xr:uid="{3521085D-1DF1-4A36-AD28-DFBFAC9A15AC}"/>
-    <hyperlink ref="C44" r:id="rId5" xr:uid="{E445C2AE-7998-4639-8B46-AE1076856BD2}"/>
+    <hyperlink ref="C18" r:id="rId1" xr:uid="{3A509D7C-6AAA-4478-ADA1-CE6211C4275B}"/>
+    <hyperlink ref="C24" r:id="rId2" xr:uid="{268D41A2-A732-4CD5-A111-A8AF6CB1EF8D}"/>
+    <hyperlink ref="C33" r:id="rId3" xr:uid="{D29A384B-38C2-4AD0-BF57-535640A666C4}"/>
+    <hyperlink ref="C37" r:id="rId4" xr:uid="{3521085D-1DF1-4A36-AD28-DFBFAC9A15AC}"/>
+    <hyperlink ref="C45" r:id="rId5" xr:uid="{E445C2AE-7998-4639-8B46-AE1076856BD2}"/>
     <hyperlink ref="A3" location="ブラックボックステスト!A10" display="①正常系を用いた一通りの流れのチェック" xr:uid="{66CD2A9B-1A7C-410E-B95A-7072E0FFE8D3}"/>
     <hyperlink ref="A4" location="ブラックボックステスト!A22" display="②入力必須エラーが正しく出るかチェック" xr:uid="{4ECA5742-2FE9-47C3-BA5F-E1F112BBB4B2}"/>
     <hyperlink ref="A5" location="ブラックボックステスト!A26" display="③名前の文字数チェック（正常系の境界値：20文字）" xr:uid="{032A2E23-2FE2-4B2A-977A-1FBCE98FA354}"/>
     <hyperlink ref="A6" location="ブラックボックステスト!A30" display="④名前の文字数チェック（異常系の境界値：21文字）" xr:uid="{52F21D79-F2B5-4349-8F1E-554BA27F7329}"/>
     <hyperlink ref="A7" location="ブラックボックステスト!A34" display="⑤メールアドレスの形式エラーが正しく出るかチェック" xr:uid="{B923A1ED-842F-4F7D-BEE8-808991124684}"/>
     <hyperlink ref="A8" location="ブラックボックステスト!A38" display="⑥電話番号の形式エラーが正しく出るかチェック" xr:uid="{E8957687-BD25-4FC1-A76F-BD13DED4FAEE}"/>
-    <hyperlink ref="I13" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{D5114FC7-508E-4B07-8734-A9FDF3F0D229}"/>
-    <hyperlink ref="I25" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{534C6B46-2778-4DF1-9222-0775496449A7}"/>
-    <hyperlink ref="I29" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{4D4B8236-F4C8-48D1-9376-80DD9D21E0D7}"/>
-    <hyperlink ref="I33" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{5AAEBD1E-6D3D-4894-B816-7094B8852302}"/>
-    <hyperlink ref="I37" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{49506B4B-EB38-462A-9823-74488B65108D}"/>
-    <hyperlink ref="I41" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{29AC62C4-977F-434C-B418-70D274F23AF7}"/>
-    <hyperlink ref="C48" r:id="rId6" xr:uid="{6798A490-9A31-48A6-BCA0-BA97DDE1492B}"/>
-    <hyperlink ref="C52" r:id="rId7" xr:uid="{CD8DEF8E-ACB6-4A14-B9B8-F6E647E4F9B1}"/>
-    <hyperlink ref="C56" r:id="rId8" xr:uid="{4B17CFFE-5E79-43D3-96DD-F4D2C3AA02D6}"/>
+    <hyperlink ref="I14" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{D5114FC7-508E-4B07-8734-A9FDF3F0D229}"/>
+    <hyperlink ref="I26" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{534C6B46-2778-4DF1-9222-0775496449A7}"/>
+    <hyperlink ref="I30" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{4D4B8236-F4C8-48D1-9376-80DD9D21E0D7}"/>
+    <hyperlink ref="I34" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{5AAEBD1E-6D3D-4894-B816-7094B8852302}"/>
+    <hyperlink ref="I38" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{49506B4B-EB38-462A-9823-74488B65108D}"/>
+    <hyperlink ref="I42" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{29AC62C4-977F-434C-B418-70D274F23AF7}"/>
+    <hyperlink ref="C49" r:id="rId6" xr:uid="{6798A490-9A31-48A6-BCA0-BA97DDE1492B}"/>
+    <hyperlink ref="C53" r:id="rId7" xr:uid="{CD8DEF8E-ACB6-4A14-B9B8-F6E647E4F9B1}"/>
+    <hyperlink ref="C57" r:id="rId8" xr:uid="{4B17CFFE-5E79-43D3-96DD-F4D2C3AA02D6}"/>
     <hyperlink ref="A9" location="ブラックボックステスト!A45" display="⑦同じメールアドレスが登録されていた場合のエラーチェック" xr:uid="{0F02ECD7-A6BA-44BF-A55F-DCC56CECE266}"/>
     <hyperlink ref="A10" location="ブラックボックステスト!A49" display="⑧同じ電話番号が登録されていた場合のエラーチェック" xr:uid="{298276B0-CE79-4A4C-9132-EFB29453C126}"/>
     <hyperlink ref="A11" location="ブラックボックステスト!A53" display="⑨同じメールアドレスかつ同じ電話番号が登録されていた場合のエラーチェック" xr:uid="{7C40F3E6-DC6A-4C80-AD6D-FEA1A2DEB489}"/>
-    <hyperlink ref="I45" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{58481281-7845-4E0B-B26B-4C4A31D3B3D1}"/>
-    <hyperlink ref="I49" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{A6993151-D69B-4DC2-A480-1C1411EAF989}"/>
-    <hyperlink ref="I53" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{85C4F0E6-D6A6-4489-8DD4-16965B4292FF}"/>
+    <hyperlink ref="I46" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{58481281-7845-4E0B-B26B-4C4A31D3B3D1}"/>
+    <hyperlink ref="I50" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{A6993151-D69B-4DC2-A480-1C1411EAF989}"/>
+    <hyperlink ref="I54" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{85C4F0E6-D6A6-4489-8DD4-16965B4292FF}"/>
+    <hyperlink ref="A12" location="ブラックボックステスト!A58" display="⑩ホーム画面の「従業員一覧」から登録画面への遷移チェック" xr:uid="{D881F577-0503-48B3-8B0B-AD203DF42167}"/>
+    <hyperlink ref="I58" location="ブラックボックステスト!A2" display="目次に戻る" xr:uid="{03BD5009-8A81-4426-BFAC-110EC66241D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId9"/>

--- a/docs/03_test/従業員登録のテストケース.xlsx
+++ b/docs/03_test/従業員登録のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FED9D80-042C-4F53-A6EC-D53F4F9EBE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F0702B-274C-4065-817B-FA1BA2C8183C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DF2BF7D9-86FA-42E4-9DEC-CF3346CAE84A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="76">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -93,16 +93,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員登録(入力)画面に遷移する</t>
-    <rPh sb="9" eb="11">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>総務部</t>
     <rPh sb="0" eb="3">
       <t>ソウムブ</t>
@@ -183,19 +173,6 @@
       <t>トウロク</t>
     </rPh>
     <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>続けて入力するボタンを押す</t>
-    <rPh sb="0" eb="1">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -286,25 +263,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員登録単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>スザキ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>チホコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストケース① 正常系を用いた一通りの流れのチェック</t>
     <rPh sb="8" eb="11">
       <t>セイジョウケイ</t>
@@ -729,67 +687,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>⑩ホーム画面の「従業員一覧」から登録画面への遷移チェック</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホーム画面の従業員管理ボタンを押す</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧に遷移する</t>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>新規従業員の登録ボタンを押す</t>
-    <rPh sb="0" eb="5">
-      <t>シンキジュウギョウイン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>登録画面に遷移する</t>
     <rPh sb="0" eb="4">
       <t>トウロクガメン</t>
@@ -800,22 +697,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の「従業員登録」ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>高橋太郎</t>
     <rPh sb="0" eb="2">
       <t>タカハシ</t>
@@ -830,35 +711,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧を確認するボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストケース⑨ 同じメールアドレス&amp;電話番号が登録されていた場合</t>
     <rPh sb="8" eb="9">
       <t>オナ</t>
@@ -890,6 +742,126 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録単体UIテスト 須崎千穂子</t>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スザキ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>チホコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑩ホーム画面の「社員一覧」から登録画面への遷移チェック</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の「社員登録」ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録(入力)画面に遷移する</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧を確認するボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面の社員管理ボタンを押す</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規社員の登録ボタンを押す</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続けて登録するボタンを押す</t>
+    <rPh sb="0" eb="1">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -998,11 +970,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1010,20 +982,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1053,17 +1025,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2609273</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47169</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1576731</xdr:rowOff>
+      <xdr:rowOff>1238250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E0B3FC4-B033-C6EA-B13A-5BB510C64F65}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F2D923A-4622-5F10-99A3-99DD098131A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1079,8 +1051,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="4006273"/>
-          <a:ext cx="2609273" cy="1576731"/>
+          <a:off x="10350500" y="3905250"/>
+          <a:ext cx="4095294" cy="1238250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1094,20 +1066,20 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2817091</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>470085</xdr:rowOff>
+      <xdr:rowOff>97289</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92E89483-DD7A-DD2E-41A0-53DEF3D00764}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E0098C2-EF05-D70A-401C-5D5E69281FBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1123,8 +1095,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="5738092"/>
-          <a:ext cx="2817091" cy="1278266"/>
+          <a:off x="10350500" y="5635625"/>
+          <a:ext cx="4064000" cy="906914"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1138,20 +1110,20 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574839</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>426238</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>1581727</xdr:rowOff>
+      <xdr:rowOff>1349375</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01694564-A783-875C-02C7-8750AC97DA15}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F71900B-F788-ECB6-14F6-99E9FA8DFA4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1167,8 +1139,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="7354455"/>
-          <a:ext cx="2574839" cy="1581727"/>
+          <a:off x="10350500" y="7254876"/>
+          <a:ext cx="4474363" cy="1349374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1185,17 +1157,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2817091</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>1278266</xdr:rowOff>
+      <xdr:rowOff>906914</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="16" name="図 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F103663-B27B-4AB5-AC21-F7DE3DD3FCA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F1491BD-A6AE-4EA7-BBBA-400F983409D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1211,8 +1183,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="9086273"/>
-          <a:ext cx="2817091" cy="1278266"/>
+          <a:off x="10350500" y="8985250"/>
+          <a:ext cx="4064000" cy="906914"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1226,20 +1198,20 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2792145</xdr:colOff>
+      <xdr:colOff>3825875</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1339273</xdr:rowOff>
+      <xdr:rowOff>920377</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="20" name="図 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95BC963-C140-DFD5-0F0C-EA08271EBD67}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6543EF5D-4AC7-7D13-CA93-9DE76AFB0685}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1255,8 +1227,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="10818091"/>
-          <a:ext cx="2792145" cy="1339273"/>
+          <a:off x="10350500" y="10715626"/>
+          <a:ext cx="3825875" cy="920376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1274,16 +1246,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2620819</xdr:colOff>
+      <xdr:colOff>3952875</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>1612813</xdr:rowOff>
+      <xdr:rowOff>1216109</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="21" name="図 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{180C5E17-5905-0478-A8AF-8435DBFD309F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E38B8094-183A-199E-1784-43BE335D7934}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1299,8 +1271,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="12549910"/>
-          <a:ext cx="2620819" cy="1612812"/>
+          <a:off x="10350500" y="12446001"/>
+          <a:ext cx="3952875" cy="1216108"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1312,22 +1284,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2690091</xdr:colOff>
+      <xdr:colOff>3683000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>459025</xdr:rowOff>
+      <xdr:rowOff>334038</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED64F671-2A0F-22E0-FB1D-4A686371F009}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABEA7FB7-6C47-AEDB-DA5A-A2027D9E434D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1343,8 +1315,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="14281727"/>
-          <a:ext cx="2690091" cy="1301843"/>
+          <a:off x="10398125" y="14176375"/>
+          <a:ext cx="3635375" cy="842038"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1356,22 +1328,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>158750</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2528455</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>24444</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>1604320</xdr:rowOff>
+      <xdr:rowOff>1270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98CD5786-8E25-F8E3-D203-7233D78E5BFB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6016FDB-1494-9AC3-9119-887A2FCA058C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1387,8 +1359,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="15967364"/>
-          <a:ext cx="2528455" cy="1604320"/>
+          <a:off x="10509250" y="15938500"/>
+          <a:ext cx="3913819" cy="1190625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1400,22 +1372,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>470578</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D8AA52-0923-B109-3FDC-EA3B1BF0C045}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CF48893-16A2-2216-13AD-70FAF5BD03B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1431,8 +1403,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="18276455"/>
-          <a:ext cx="2574637" cy="1618019"/>
+          <a:off x="10398125" y="20018375"/>
+          <a:ext cx="4000500" cy="1359578"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1445,21 +1417,373 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2736273</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>891093</xdr:rowOff>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="25" name="図 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A27E57CA-D631-E237-3EC7-DE2366321078}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BEA9719-AFE7-4705-A55D-CFF3326AC570}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="18161000"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="図 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF729D69-AF35-48C6-B454-8D448F6C476D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="22717125"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F25B4CAC-20B7-4016-B2A0-F527B9BF41C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="26987500"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{369A645F-1D54-4969-A683-89D8E50DFB19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="30924500"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="図 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8685AF50-2D17-449C-8185-A0007C25CEDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="35290125"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="図 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2277C06A-3E14-4C45-9182-1BC5F789DABF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="39052500"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="図 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C259BC1A-B46F-4AAA-B0C0-D01AC6BDEF45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="42624375"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1216108</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="図 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F86898-7436-43DF-BB87-904990261C18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10350500" y="46863000"/>
+          <a:ext cx="3952875" cy="1216108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>928717</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFA0BCE-5B0B-3D1E-A8ED-317A72C000CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1475,8 +1799,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="20008273"/>
-          <a:ext cx="2736273" cy="1918638"/>
+          <a:off x="10350500" y="24431625"/>
+          <a:ext cx="4079875" cy="928717"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1489,329 +1813,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
+      <xdr:colOff>3540125</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>760071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
+        <xdr:cNvPr id="35" name="図 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11BCF753-276F-4BF4-AE46-37DB7684307B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="22860000"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43DFC006-61B6-4E6D-89B2-D222E5CF4091}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="27143364"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>1656</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69D19386-E921-4EAB-8281-A10D0C154766}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="31103455"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E35BA470-B1ED-4229-B3D2-CAF38CD33B31}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="35444545"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="図 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52836F56-21F4-4431-9354-719A5D685058}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="39219909"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="図 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F217B490-4674-49FF-BAF4-45F03A62543A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="42487273"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2574637</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>1618019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="図 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBFFD681-EAB9-4A4B-9D24-3679CE890775}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568545" y="46666727"/>
-          <a:ext cx="2574637" cy="1618019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2805547</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>475371</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="図 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7779188B-268D-FBAD-419A-F7C38A52062C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33936259-B986-D6C5-1084-DAFDA2E83CB8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1827,8 +1843,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568546" y="24580273"/>
-          <a:ext cx="2805546" cy="1445189"/>
+          <a:off x="10350500" y="28702001"/>
+          <a:ext cx="3540125" cy="1585570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1841,21 +1857,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2043546</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>765582</xdr:rowOff>
+      <xdr:colOff>3873500</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>748010</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="図 41">
+        <xdr:cNvPr id="36" name="図 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951DCF5A-1E6B-98E0-F7FC-525AF5065C75}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA4F21B-E3E0-D668-2EB4-562ECDFA2612}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1871,8 +1887,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="28863636"/>
-          <a:ext cx="2043546" cy="1596855"/>
+          <a:off x="10350500" y="32543750"/>
+          <a:ext cx="3873500" cy="1748135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1885,21 +1901,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2765066</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>577274</xdr:rowOff>
+      <xdr:colOff>3175000</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>688547</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="図 42">
+        <xdr:cNvPr id="50" name="図 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE66843-53BF-9D32-9322-A42BDE4552E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CB9D0E5-2372-57F2-BBDE-63A65415ACA7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1915,8 +1931,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="32719819"/>
-          <a:ext cx="2765066" cy="1570182"/>
+          <a:off x="10350500" y="37020500"/>
+          <a:ext cx="3175000" cy="1482297"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1928,22 +1944,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2378364</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>706761</xdr:rowOff>
+      <xdr:colOff>3460751</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>739285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="図 43">
+        <xdr:cNvPr id="51" name="図 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D2D219-EAD6-75B6-378C-8EA64635821E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{191A7B36-722E-5265-4915-0F1DCCBA224D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1959,8 +1975,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="37176364"/>
-          <a:ext cx="2378364" cy="1503397"/>
+          <a:off x="10350501" y="40798751"/>
+          <a:ext cx="3460750" cy="1628284"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1973,21 +1989,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>600900</xdr:rowOff>
+      <xdr:colOff>2930519</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>666749</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="図 44">
+        <xdr:cNvPr id="53" name="図 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E84E97F5-62E9-78FD-BD9E-1B2D265B337F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F80C07-CD54-4982-8CCB-4770A464371F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2003,8 +2019,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568545" y="40974818"/>
-          <a:ext cx="1951182" cy="1270537"/>
+          <a:off x="10350500" y="49180750"/>
+          <a:ext cx="2930519" cy="1539874"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2016,22 +2032,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>57728</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2670993</xdr:colOff>
+      <xdr:colOff>3349625</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>796636</xdr:rowOff>
+      <xdr:rowOff>708205</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="図 45">
+        <xdr:cNvPr id="54" name="図 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE49798D-A44C-9251-C926-62AE11A119FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D83472-E499-C55A-ED58-5BC3063ABBB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2047,8 +2063,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11626273" y="44704000"/>
-          <a:ext cx="2613265" cy="1685636"/>
+          <a:off x="10350500" y="44973875"/>
+          <a:ext cx="3349625" cy="1597205"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2060,22 +2076,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2343729</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>835998</xdr:rowOff>
+      <xdr:colOff>3667125</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1625519</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="図 46">
+        <xdr:cNvPr id="55" name="図 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4363D7AA-8D68-297B-1945-D3BE4EF0A64F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9109E9D-2684-BE9C-9405-20C4EE9D4F8D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2091,8 +2107,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568546" y="48918091"/>
-          <a:ext cx="2343728" cy="1701907"/>
+          <a:off x="10350500" y="51308001"/>
+          <a:ext cx="3667125" cy="1625518"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2104,22 +2120,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2678547</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1281856</xdr:rowOff>
+      <xdr:colOff>3302000</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>1412661</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="図 47">
+        <xdr:cNvPr id="56" name="図 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57D82C9A-E1CE-0C6B-5930-6B886CAAF569}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BC26570-F528-7C96-6C7E-6701217E6C1D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2135,52 +2151,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11568546" y="51030909"/>
-          <a:ext cx="2678546" cy="1281856"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2793057</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>11546</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="図 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BB69F41-9CEA-E2AF-BA36-1129497FD459}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11568546" y="52716545"/>
-          <a:ext cx="2793056" cy="1604819"/>
+          <a:off x="10350500" y="52990751"/>
+          <a:ext cx="3302000" cy="1412660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2492,19 +2464,19 @@
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="12"/>
+    <col min="1" max="1" width="8.6640625" style="6"/>
     <col min="2" max="2" width="14.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="9" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="54.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="37.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.4140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="53.1640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="8" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -2514,8 +2486,8 @@
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="12" t="s">
-        <v>50</v>
+      <c r="A2" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2525,8 +2497,8 @@
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="13" t="s">
-        <v>41</v>
+      <c r="A3" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2536,8 +2508,8 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
-        <v>42</v>
+      <c r="A4" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2547,8 +2519,8 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="13" t="s">
-        <v>43</v>
+      <c r="A5" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2558,8 +2530,8 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="13" t="s">
-        <v>44</v>
+      <c r="A6" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2569,8 +2541,8 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13" t="s">
-        <v>45</v>
+      <c r="A7" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2580,8 +2552,8 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="13" t="s">
-        <v>46</v>
+      <c r="A8" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2591,8 +2563,8 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13" t="s">
-        <v>62</v>
+      <c r="A9" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2602,8 +2574,8 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13" t="s">
-        <v>63</v>
+      <c r="A10" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2613,8 +2585,8 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13" t="s">
-        <v>64</v>
+      <c r="A11" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2624,8 +2596,8 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="13" t="s">
-        <v>65</v>
+      <c r="A12" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2643,26 +2615,26 @@
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="A14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="12" t="s">
-        <v>49</v>
+      <c r="A15" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -2672,26 +2644,26 @@
         <v>6</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="12">
+      <c r="A16" s="6">
         <v>1</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="17" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="14">
+      <c r="A17" s="11">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -2706,93 +2678,93 @@
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="10" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:9" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="G18" s="10"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="12">
+      <c r="A19" s="6">
         <v>3</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="20" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="12">
+      <c r="A20" s="6">
         <v>4</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="B20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="12">
+      <c r="A21" s="6">
         <v>5</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="22" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="12">
+      <c r="A22" s="6">
         <v>6</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="66.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="11">
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -2808,74 +2780,74 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="66.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="14"/>
+    <row r="24" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="11"/>
       <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="12">
+      <c r="A25" s="6">
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
+      <c r="A26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="12">
+      <c r="A27" s="6">
         <v>1</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="28" spans="1:9" ht="80.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="14">
+      <c r="A28" s="11">
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -2890,53 +2862,53 @@
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>25</v>
+      <c r="G28" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="80.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="14"/>
+      <c r="A29" s="11"/>
       <c r="C29" s="5"/>
       <c r="E29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+      <c r="A30" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
       <c r="I30" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="12">
+      <c r="A31" s="6">
         <v>1</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="14">
+      <c r="A32" s="11">
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2953,60 +2925,60 @@
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="14"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G33" s="9"/>
     </row>
     <row r="34" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
+      <c r="A34" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
       <c r="I34" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="135.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="12">
+      <c r="A35" s="6">
         <v>1</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="36" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="14">
+      <c r="A36" s="11">
         <v>2</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -3023,60 +2995,60 @@
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="65.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="14"/>
+      <c r="A37" s="11"/>
       <c r="B37" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:9" ht="45.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
       <c r="I38" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="12">
+      <c r="A39" s="6">
         <v>1</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="40" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="14">
+      <c r="A40" s="11">
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -3095,58 +3067,58 @@
       <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="78.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="14"/>
+      <c r="A41" s="11"/>
       <c r="B41" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G41" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
+      <c r="A42" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
       <c r="I42" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="136.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="12">
+      <c r="A43" s="6">
         <v>1</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="44" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="14">
+      <c r="A44" s="11">
         <v>2</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -3164,58 +3136,58 @@
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="14"/>
+      <c r="A45" s="11"/>
       <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G45" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
+      <c r="A46" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
       <c r="I46" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="138" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="12">
+      <c r="A47" s="6">
         <v>1</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="14">
+    </row>
+    <row r="48" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="11">
         <v>2</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -3232,59 +3204,59 @@
       </c>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="14"/>
+    <row r="49" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="11"/>
       <c r="B49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="50" spans="1:9" ht="38.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
+      <c r="A50" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
       <c r="I50" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="150" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="12">
+      <c r="A51" s="6">
         <v>1</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="52" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="14">
+      <c r="A52" s="11">
         <v>2</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -3302,58 +3274,58 @@
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="14"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G53" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
+      <c r="A54" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
       <c r="I54" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="148" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="12">
+      <c r="A55" s="6">
         <v>1</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="56" spans="1:9" ht="68.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="14">
+      <c r="A56" s="11">
         <v>2</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -3371,69 +3343,69 @@
       <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="68.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="14"/>
+      <c r="A57" s="11"/>
       <c r="B57" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G57" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+      <c r="A58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
       <c r="I58" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="133" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="12">
+      <c r="A59" s="6">
         <v>1</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
+      <c r="B59" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
       <c r="G59" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="125" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="12">
+      <c r="A60" s="6">
         <v>2</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3444,7 +3416,16 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="H17:H18"/>
@@ -3456,7 +3437,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A44:A45"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B43:F43"/>
@@ -3472,15 +3452,7 @@
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B35:F35"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="A14:H14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
